--- a/premise/data/additional_inventories/lci-fuel_cell.xlsx
+++ b/premise/data/additional_inventories/lci-fuel_cell.xlsx
@@ -1345,8 +1345,10 @@
       <c r="A25" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="B25" s="12" t="s">
-        <v>115</v>
+      <c r="B25" s="12" t="inlineStr">
+        <is>
+          <t>LCI for a PEMFC fuel cell stack. Original size: 48 kWe, but normalized here to 1 kWe. Regarding geographical and time scope, production in Europe was considered based on current conditions. The reference year of the data is 2021 and data sets could be considered valid until 2024. The stack consists of 280 membrane electrode assembly (MEA) units with an active area of 200 cm2 each. The amount of Pt in the stack is 0.5425 g/kW, with a power density of 1.36 kW/kg. Operational time was set to 20,000 h at power of 1 kWe. Due to the degradation effects the hydrogen consumption must be increased to always generate the power of 1 kWe. In the case of dynamic operational regime 5 replacements (Nd = 5) of the PEMFC stack are included (lifetime of 3'800 hours per stack). Local PEMFC stack steel-identity correction, 2026-10-17 (approved). Mori et al. (2023), Life cycle sustainability assessment of a proton exchange membrane fuel cell technology for ecodesign purposes, DOI 10.1016/j.ijhydene.2023.05.255, Table 1, printed page 39676 (PDF page 4). https://repozitorij.uni-lj.si/Dokument.php?id=178494&amp;lang=slv The Steel product row reports 2.820 kg per 48 kWe stack, or 58.75 g/kWe, linked to DE: EAF Steel billet/Slab/Bloom Sphera. It is separate from the source stainless (450.47 g/kWe) and chromium-steel (17.75 g/kWe) entries. Replace only this 58.75 g input with steel production, electric, low-alloyed, Europe without Switzerland and Austria; product steel, low-alloyed. This ecoinvent European ordinary EAF-steel activity is a regional and grade proxy for the source German Sphera steel, not the identical source process or a documented exact alloy composition. Retain the original =58.75/1000 kg per 1 kWe stack formula, reference output, separate stainless inputs, steel-working service and other manufacturing coefficients. Inherited quantity uncertainty/pedigree fields are retained and do not quantify this supplier-proxy uncertainty. No added fabrication or yield factor, changed stack lifetime, or new primary/secondary trajectory. This mapping correction does not validate the complete stack, practical metal yields or suitability of the source 2021 light-vehicle design for other vehicles and future years.</t>
+        </is>
       </c>
       <c r="K25" s="13"/>
       <c r="L25" s="13"/>
@@ -2201,15 +2203,19 @@
       </c>
     </row>
     <row r="42" spans="1:18" s="12" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A42" s="12" t="s">
-        <v>65</v>
+      <c r="A42" s="12" t="inlineStr">
+        <is>
+          <t>steel production, electric, low-alloyed</t>
+        </is>
       </c>
       <c r="B42" s="12">
         <f>58.75/1000</f>
         <v>5.8749999999999997E-2</v>
       </c>
-      <c r="C42" s="12" t="s">
-        <v>16</v>
+      <c r="C42" s="12" t="inlineStr">
+        <is>
+          <t>Europe without Switzerland and Austria</t>
+        </is>
       </c>
       <c r="D42" s="12" t="s">
         <v>13</v>
@@ -2217,8 +2223,10 @@
       <c r="F42" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="G42" s="12" t="s">
-        <v>66</v>
+      <c r="G42" s="12" t="inlineStr">
+        <is>
+          <t>steel, low-alloyed</t>
+        </is>
       </c>
       <c r="I42" s="12">
         <v>2</v>
@@ -2251,6 +2259,11 @@
       <c r="R42">
         <f t="shared" si="11"/>
         <v>0.47095746419981693</v>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Local PEMFC stack steel-identity correction, 2026-10-17 (approved). Mori et al. (2023), Life cycle sustainability assessment of a proton exchange membrane fuel cell technology for ecodesign purposes, DOI 10.1016/j.ijhydene.2023.05.255, Table 1, printed page 39676 (PDF page 4). https://repozitorij.uni-lj.si/Dokument.php?id=178494&amp;lang=slv The Steel product row reports 2.820 kg per 48 kWe stack, or 58.75 g/kWe, linked to DE: EAF Steel billet/Slab/Bloom Sphera. It is separate from the source stainless (450.47 g/kWe) and chromium-steel (17.75 g/kWe) entries. Replace only this 58.75 g input with steel production, electric, low-alloyed, Europe without Switzerland and Austria; product steel, low-alloyed. This ecoinvent European ordinary EAF-steel activity is a regional and grade proxy for the source German Sphera steel, not the identical source process or a documented exact alloy composition. Retain the original =58.75/1000 kg per 1 kWe stack formula, reference output, separate stainless inputs, steel-working service and other manufacturing coefficients. Inherited quantity uncertainty/pedigree fields are retained and do not quantify this supplier-proxy uncertainty. No added fabrication or yield factor, changed stack lifetime, or new primary/secondary trajectory. This mapping correction does not validate the complete stack, practical metal yields or suitability of the source 2021 light-vehicle design for other vehicles and future years.</t>
+        </is>
       </c>
     </row>
     <row r="43" spans="1:18" s="12" customFormat="1" ht="16" x14ac:dyDescent="0.2">

--- a/premise/data/additional_inventories/lci-fuel_cell.xlsx
+++ b/premise/data/additional_inventories/lci-fuel_cell.xlsx
@@ -2484,8 +2484,10 @@
       <c r="A53" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="B53" s="12" t="s">
-        <v>116</v>
+      <c r="B53" s="12" t="inlineStr">
+        <is>
+          <t>LCI for a PEMFC fuel cell Balance of Plant. Operational time was set to 20,000 h at power of 1 kWe. Due to the degradation effects the hydrogen consumption must be increased to always generate the power of 1 kWe. In the case of dynamic operational regime 5 replacements (Nd = 5) of the PEMFC stack are included (lifetime of 3'800 hours per stack). Local PEMFC balance-of-plant steel-identity correction, 2026-10-17 (approved). Stropnik et al. (2022), The influence of degradation effects in proton exchange membrane fuel cells on life cycle assessment modelling and environmental impact indicators, DOI 10.1016/j.ijhydene.2022.04.011, Table 1, printed page 24231 (PDF page 9), https://repozitorij.uni-lj.si/Dokument.php?id=159610&amp;lang=eng. The source BoP Steel product row specifies 3.7 kg per 1 kWe PEMFC system, linked to DE: EAF Steel billet/Slab/Bloom ts, separately from 1.1 kg chromium steel. Replace only the 3.7 kg material supplier with steel production, electric, low-alloyed, Europe without Switzerland and Austria; product steel, low-alloyed. This is an ecoinvent European regional and grade proxy for the source German EAF process, not the identical source dataset or a documented exact alloy composition. Retain 3.7 kg per 1 kWe BoP unit, the separate 1.1 kg stainless input, metal-working services, reference output and all other amounts. Inherited quantity uncertainty/pedigree fields are retained and do not quantify supplier-proxy uncertainty. No new fabrication, yield, BoP mass normalization, stack/BoP replacement multiplier or future primary/secondary trajectory. This corrects one material identity; it does not reconcile the exported equipment mass, independently validate manufacturing yields or establish suitability for other fuel-cell designs.</t>
+        </is>
       </c>
       <c r="K53" s="13"/>
       <c r="L53" s="13"/>
@@ -2595,14 +2597,18 @@
       <c r="P56" s="13"/>
     </row>
     <row r="57" spans="1:20" s="12" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A57" s="12" t="s">
-        <v>65</v>
+      <c r="A57" s="12" t="inlineStr">
+        <is>
+          <t>steel production, electric, low-alloyed</t>
+        </is>
       </c>
       <c r="B57" s="12">
         <v>3.7</v>
       </c>
-      <c r="C57" s="12" t="s">
-        <v>16</v>
+      <c r="C57" s="12" t="inlineStr">
+        <is>
+          <t>Europe without Switzerland and Austria</t>
+        </is>
       </c>
       <c r="D57" s="12" t="s">
         <v>13</v>
@@ -2610,8 +2616,10 @@
       <c r="F57" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="G57" s="12" t="s">
-        <v>66</v>
+      <c r="G57" s="12" t="inlineStr">
+        <is>
+          <t>steel, low-alloyed</t>
+        </is>
       </c>
       <c r="I57" s="12">
         <v>2</v>
@@ -2654,6 +2662,11 @@
 )
 )))</f>
         <v>0.47095746419981693</v>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Local PEMFC balance-of-plant steel-identity correction, 2026-10-17 (approved). Stropnik et al. (2022), The influence of degradation effects in proton exchange membrane fuel cells on life cycle assessment modelling and environmental impact indicators, DOI 10.1016/j.ijhydene.2022.04.011, Table 1, printed page 24231 (PDF page 9), https://repozitorij.uni-lj.si/Dokument.php?id=159610&amp;lang=eng. The source BoP Steel product row specifies 3.7 kg per 1 kWe PEMFC system, linked to DE: EAF Steel billet/Slab/Bloom ts, separately from 1.1 kg chromium steel. Replace only the 3.7 kg material supplier with steel production, electric, low-alloyed, Europe without Switzerland and Austria; product steel, low-alloyed. This is an ecoinvent European regional and grade proxy for the source German EAF process, not the identical source dataset or a documented exact alloy composition. Retain 3.7 kg per 1 kWe BoP unit, the separate 1.1 kg stainless input, metal-working services, reference output and all other amounts. Inherited quantity uncertainty/pedigree fields are retained and do not quantify supplier-proxy uncertainty. No new fabrication, yield, BoP mass normalization, stack/BoP replacement multiplier or future primary/secondary trajectory. This corrects one material identity; it does not reconcile the exported equipment mass, independently validate manufacturing yields or establish suitability for other fuel-cell designs.</t>
+        </is>
       </c>
     </row>
     <row r="58" spans="1:20" s="12" customFormat="1" ht="16" x14ac:dyDescent="0.2">

--- a/premise/data/additional_inventories/lci-fuel_cell.xlsx
+++ b/premise/data/additional_inventories/lci-fuel_cell.xlsx
@@ -1347,7 +1347,9 @@
       </c>
       <c r="B25" s="12" t="inlineStr">
         <is>
-          <t>LCI for a PEMFC fuel cell stack. Original size: 48 kWe, but normalized here to 1 kWe. Regarding geographical and time scope, production in Europe was considered based on current conditions. The reference year of the data is 2021 and data sets could be considered valid until 2024. The stack consists of 280 membrane electrode assembly (MEA) units with an active area of 200 cm2 each. The amount of Pt in the stack is 0.5425 g/kW, with a power density of 1.36 kW/kg. Operational time was set to 20,000 h at power of 1 kWe. Due to the degradation effects the hydrogen consumption must be increased to always generate the power of 1 kWe. In the case of dynamic operational regime 5 replacements (Nd = 5) of the PEMFC stack are included (lifetime of 3'800 hours per stack). Local PEMFC stack steel-identity correction, 2026-10-17 (approved). Mori et al. (2023), Life cycle sustainability assessment of a proton exchange membrane fuel cell technology for ecodesign purposes, DOI 10.1016/j.ijhydene.2023.05.255, Table 1, printed page 39676 (PDF page 4). https://repozitorij.uni-lj.si/Dokument.php?id=178494&amp;lang=slv The Steel product row reports 2.820 kg per 48 kWe stack, or 58.75 g/kWe, linked to DE: EAF Steel billet/Slab/Bloom Sphera. It is separate from the source stainless (450.47 g/kWe) and chromium-steel (17.75 g/kWe) entries. Replace only this 58.75 g input with steel production, electric, low-alloyed, Europe without Switzerland and Austria; product steel, low-alloyed. This ecoinvent European ordinary EAF-steel activity is a regional and grade proxy for the source German Sphera steel, not the identical source process or a documented exact alloy composition. Retain the original =58.75/1000 kg per 1 kWe stack formula, reference output, separate stainless inputs, steel-working service and other manufacturing coefficients. Inherited quantity uncertainty/pedigree fields are retained and do not quantify this supplier-proxy uncertainty. No added fabrication or yield factor, changed stack lifetime, or new primary/secondary trajectory. This mapping correction does not validate the complete stack, practical metal yields or suitability of the source 2021 light-vehicle design for other vehicles and future years.</t>
+          <t>APPROVED PEMFC ETHOXYLATED-ALCOHOL SOURCE MATCH, 2026-10-18. Mori et al. (2023), DOI 10.1016/j.ijhydene.2023.05.255, Table 1, printed page 39676 (https://repozitorij.uni-lj.si/Dokument.php?id=178494&amp;lang=slv), specifies C12-15 Alcohol (petro) Ethoxylate, 7 mol EO, 4.58 g/kWe. Replace AE&gt;20 with existing ethoxylated alcohol (AE7) production, petrochemical, RER. Retain =4.58/1000 kg/kWe, uncertainty and all other stack inputs. This European petrochemical supplier is a chemical-class and route proxy; exact chain-length distribution and measured supply are not established. No change to stack lifetime, platinum loading or any future reduction.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+LCI for a PEMFC fuel cell stack. Original size: 48 kWe, but normalized here to 1 kWe. Regarding geographical and time scope, production in Europe was considered based on current conditions. The reference year of the data is 2021 and data sets could be considered valid until 2024. The stack consists of 280 membrane electrode assembly (MEA) units with an active area of 200 cm2 each. The amount of Pt in the stack is 0.5425 g/kW, with a power density of 1.36 kW/kg. Operational time was set to 20,000 h at power of 1 kWe. Due to the degradation effects the hydrogen consumption must be increased to always generate the power of 1 kWe. In the case of dynamic operational regime 5 replacements (Nd = 5) of the PEMFC stack are included (lifetime of 3'800 hours per stack). Local PEMFC stack steel-identity correction, 2026-10-17 (approved). Mori et al. (2023), Life cycle sustainability assessment of a proton exchange membrane fuel cell technology for ecodesign purposes, DOI 10.1016/j.ijhydene.2023.05.255, Table 1, printed page 39676 (PDF page 4). https://repozitorij.uni-lj.si/Dokument.php?id=178494&amp;lang=slv The Steel product row reports 2.820 kg per 48 kWe stack, or 58.75 g/kWe, linked to DE: EAF Steel billet/Slab/Bloom Sphera. It is separate from the source stainless (450.47 g/kWe) and chromium-steel (17.75 g/kWe) entries. Replace only this 58.75 g input with steel production, electric, low-alloyed, Europe without Switzerland and Austria; product steel, low-alloyed. This ecoinvent European ordinary EAF-steel activity is a regional and grade proxy for the source German Sphera steel, not the identical source process or a documented exact alloy composition. Retain the original =58.75/1000 kg per 1 kWe stack formula, reference output, separate stainless inputs, steel-working service and other manufacturing coefficients. Inherited quantity uncertainty/pedigree fields are retained and do not quantify this supplier-proxy uncertainty. No added fabrication or yield factor, changed stack lifetime, or new primary/secondary trajectory. This mapping correction does not validate the complete stack, practical metal yields or suitability of the source 2021 light-vehicle design for other vehicles and future years.</t>
         </is>
       </c>
       <c r="K25" s="13"/>
@@ -1925,15 +1927,19 @@
       </c>
     </row>
     <row r="37" spans="1:18" s="12" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A37" s="12" t="s">
-        <v>120</v>
+      <c r="A37" s="12" t="inlineStr">
+        <is>
+          <t>ethoxylated alcohol (AE7) production, petrochemical</t>
+        </is>
       </c>
       <c r="B37" s="12">
         <f>4.58/1000</f>
         <v>4.5799999999999999E-3</v>
       </c>
-      <c r="C37" s="12" t="s">
-        <v>16</v>
+      <c r="C37" s="12" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
       </c>
       <c r="D37" s="12" t="s">
         <v>13</v>
@@ -1941,8 +1947,10 @@
       <c r="F37" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="G37" s="12" t="s">
-        <v>121</v>
+      <c r="G37" s="12" t="inlineStr">
+        <is>
+          <t>ethoxylated alcohol (AE7)</t>
+        </is>
       </c>
       <c r="I37" s="12">
         <v>2</v>

--- a/premise/data/additional_inventories/lci-fuel_cell.xlsx
+++ b/premise/data/additional_inventories/lci-fuel_cell.xlsx
@@ -857,7 +857,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:T366"/>
+  <dimension ref="A1:T388"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="41.1640625" customWidth="1"/>
@@ -7848,6 +7848,467 @@
       <c r="O366" s="13"/>
       <c r="P366" s="13"/>
     </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>fuel cell Balance of Plant, road mass engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B371">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>fuel cell Balance of Plant, road mass engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>Stropnik etal2022 Table1 DOI10.1016/j.ijhydene.2022.04.011 https://repozitorij.uni-lj.si/Dokument.php?id=159610&amp;lang=eng; existing vehicle exporter mass/6.6 normalization.</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>APPROVED ROAD FUEL-CELL AUXILIARY MASS REFERENCE, item27, 2026-10-18. Stropnik etal2022 Table1 DOI10.1016/j.ijhydene.2022.04.011 https://repozitorij.uni-lj.si/Dokument.php?id=159610&amp;lang=eng; existing vehicle exporter mass/6.6 normalization. Existing manufacturing reference contains3.7kg plainsteel+1.5HDPE+1.1stainless+0.8iron+0.75Al+0.25PP=8.1kg/kWe; exporter divides modeled physical BoP mass by6.6, omitting the HDPE from that divisor. Gross source inputs are not automatically retained mass. Adopt explicit engineering100percent material retention reference:onekg installed roadBoP is public recipe/8.1 with separately retained forming services and16.9/8.1kWh manufacture. No measured yield or manufacturer material breakdown is claimed. Replace vehicle purchaseqold units withqold*6.6kg of this mass-based reference, recovering its modeled equipment mass. This changes selected manufacturing representation;8.1/6.6 is not a proven physical-error factor or blanket correction to generic fuel-cell inventories. Model-installed BoP mass/power remains an unvalidated sizing assumption, particularly car1.347826 andtruck1.4kg/kW versus stationary/lightvehicle source8.1kg/kW; engineering transfer is composition-by-mass, not identical source functionality. Generic1kWe recipe and its purchasers remain unchanged. Existing corrected plainsteel grade and separately specified stainless preserved. No new recovery credits or primary/secondary assumptions. Stack and BoP counts are deliberately unchanged here; independent replacement budgets are item28. Test retained-mass fraction80-100percent and alternative mobile BoP composition; functional component coverage and losses remain gaps.</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>Exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C377" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E377" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="F377" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="G377" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H377" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>fuel cell Balance of Plant, road mass engineering reference</t>
+        </is>
+      </c>
+      <c r="B378">
+        <v>1</v>
+      </c>
+      <c r="C378" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D378" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F378" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="G378" t="inlineStr">
+        <is>
+          <t>fuel cell Balance of Plant, road mass engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>steel production, electric, low-alloyed</t>
+        </is>
+      </c>
+      <c r="B379">
+        <v>0.45679012345679015</v>
+      </c>
+      <c r="C379" t="inlineStr">
+        <is>
+          <t>Europe without Switzerland and Austria</t>
+        </is>
+      </c>
+      <c r="D379" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F379" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G379" t="inlineStr">
+        <is>
+          <t>steel, low-alloyed</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>market for metal working, average for steel product manufacturing</t>
+        </is>
+      </c>
+      <c r="B380">
+        <v>0.45679012345679015</v>
+      </c>
+      <c r="C380" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D380" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F380" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G380" t="inlineStr">
+        <is>
+          <t>metal working, average for steel product manufacturing</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>market for polyethylene, high density, granulate</t>
+        </is>
+      </c>
+      <c r="B381">
+        <v>0.1851851851851852</v>
+      </c>
+      <c r="C381" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D381" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F381" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G381" t="inlineStr">
+        <is>
+          <t>polyethylene, high density, granulate</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>market for steel, chromium steel 18/8</t>
+        </is>
+      </c>
+      <c r="B382">
+        <v>0.1358024691358025</v>
+      </c>
+      <c r="C382" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F382" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G382" t="inlineStr">
+        <is>
+          <t>steel, chromium steel 18/8</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>market for metal working, average for steel product manufacturing</t>
+        </is>
+      </c>
+      <c r="B383">
+        <v>0.1358024691358025</v>
+      </c>
+      <c r="C383" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D383" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F383" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G383" t="inlineStr">
+        <is>
+          <t>metal working, average for steel product manufacturing</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>market for cast iron</t>
+        </is>
+      </c>
+      <c r="B384">
+        <v>0.09876543209876544</v>
+      </c>
+      <c r="C384" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F384" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G384" t="inlineStr">
+        <is>
+          <t>cast iron</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>market for aluminium, primary, ingot</t>
+        </is>
+      </c>
+      <c r="B385">
+        <v>0.0925925925925926</v>
+      </c>
+      <c r="C385" t="inlineStr">
+        <is>
+          <t>IAI Area, EU27 &amp; EFTA</t>
+        </is>
+      </c>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F385" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G385" t="inlineStr">
+        <is>
+          <t>aluminium, primary, ingot</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>market for metal working, average for aluminium product manufacturing</t>
+        </is>
+      </c>
+      <c r="B386">
+        <v>0.0925925925925926</v>
+      </c>
+      <c r="C386" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F386" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G386" t="inlineStr">
+        <is>
+          <t>metal working, average for aluminium product manufacturing</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>market for polypropylene, granulate</t>
+        </is>
+      </c>
+      <c r="B387">
+        <v>0.0308641975308642</v>
+      </c>
+      <c r="C387" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D387" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F387" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G387" t="inlineStr">
+        <is>
+          <t>polypropylene, granulate</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>market group for electricity, low voltage</t>
+        </is>
+      </c>
+      <c r="B388">
+        <v>2.0864197530864197</v>
+      </c>
+      <c r="C388" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>kilowatt hour</t>
+        </is>
+      </c>
+      <c r="F388" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G388" t="inlineStr">
+        <is>
+          <t>electricity, low voltage</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/premise/data/additional_inventories/lci-fuel_cell.xlsx
+++ b/premise/data/additional_inventories/lci-fuel_cell.xlsx
@@ -857,7 +857,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:T388"/>
+  <dimension ref="A1:T402"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="41.1640625" customWidth="1"/>
@@ -8309,6 +8309,227 @@
         </is>
       </c>
     </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>fuel cell system assembly, rail30kh stack engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B393">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>fuel cell system assembly, rail30kh stack engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>Knibbe2023 DOI10.1016/j.est.2023.108090, owner rail reference860kW/30000hstack and240000hoperation; Stropnik2022 DOI10.1016/j.ijhydene.2022.04.011 BoP20000h.</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>APPROVED SINGLE RAIL FUEL-CELL REPLACEMENT BUDGET, item29, 2026-10-18. Knibbe2023 DOI10.1016/j.est.2023.108090, owner rail reference860kW/30000hstack and240000hoperation; Stropnik2022 DOI10.1016/j.ijhydene.2022.04.011 BoP20000h. Existing owner buys860kW*240000/30000=6880kW-equivalent system sets. Generic assembly additionally buys20000/3800=5.2631579stacks, yielding42.105stack sets over owner life. Introduce rail-specific assembly per1kWe owner set:one existing generic manufactured stack (not generic lifetime assembly) and30000/20000=1.5genericBoP units. Therefore owner lifetime has8stacksets and12BoPsets, each budget applied once.30000h railstack life is the existing heavy-haul engineering assumption, not a demonstrated lightvehicle stack endurance; retain it explicitly rather than silently importing3800h. BoP20000h is a source-based engineering durability proxy; fractional1.5 is expected lifetime attribution, not an instantaneous1.5BoP installation. Stack and BoP manufacture/source grades/size proxies remain unchanged; generic stack remains eligible for existing future catalyst updates. No new platinum loading or primary/secondary curve. Heavy-haul power/duty/passenger representativeness, storage and battery design remain separate gaps. Existing860kW and6880owner quantity retained; the explicit final-energy hydrogen passenger-rail purchase relinked; other rail service inherits its locomotive supplier so old cached assembly identity cannot persist.</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>Exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="D399" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E399" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="F399" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="G399" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H399" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>fuel cell system assembly, rail30kh stack engineering reference</t>
+        </is>
+      </c>
+      <c r="B400">
+        <v>1</v>
+      </c>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D400" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="F400" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="G400" t="inlineStr">
+        <is>
+          <t>fuel cell system assembly, rail30kh stack engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>fuel cell stack production, 1 kWe, proton exchange membrane (PEM)</t>
+        </is>
+      </c>
+      <c r="B401">
+        <v>1</v>
+      </c>
+      <c r="C401" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D401" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="F401" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G401" t="inlineStr">
+        <is>
+          <t>fuel cell stack, 1 kWe, proton exchange membrane (PEM)</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>fuel cell Balance of Plant production, 1 kWe, proton exchange membrane (PEM)</t>
+        </is>
+      </c>
+      <c r="B402">
+        <v>1.5</v>
+      </c>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D402" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="F402" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G402" t="inlineStr">
+        <is>
+          <t>fuel cell Balance of Plant, 1 kWe, proton exchange membrane (PEM)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/premise/data/additional_inventories/lci-fuel_cell.xlsx
+++ b/premise/data/additional_inventories/lci-fuel_cell.xlsx
@@ -857,7 +857,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:T402"/>
+  <dimension ref="A1:T418"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="41.1640625" customWidth="1"/>
@@ -1347,7 +1347,9 @@
       </c>
       <c r="B25" s="12" t="inlineStr">
         <is>
-          <t>APPROVED PEMFC ETHOXYLATED-ALCOHOL SOURCE MATCH, 2026-10-18. Mori et al. (2023), DOI 10.1016/j.ijhydene.2023.05.255, Table 1, printed page 39676 (https://repozitorij.uni-lj.si/Dokument.php?id=178494&amp;lang=slv), specifies C12-15 Alcohol (petro) Ethoxylate, 7 mol EO, 4.58 g/kWe. Replace AE&gt;20 with existing ethoxylated alcohol (AE7) production, petrochemical, RER. Retain =4.58/1000 kg/kWe, uncertainty and all other stack inputs. This European petrochemical supplier is a chemical-class and route proxy; exact chain-length distribution and measured supply are not established. No change to stack lifetime, platinum loading or any future reduction.
+          <t>APPROVED PEMFC PET-FILM MATERIAL IDENTITY, item32, 2026-10-18. Mori2023 Table1 DOI10.1016/j.ijhydene.2023.05.255 https://repozitorij.uni-lj.si/Dokument.php?id=178494&amp;lang=slv specifies37.92g PETfilmwithglue/kWe, notLDPE. Keep total film/glue purchase0.03792kg/kWe. Reference1kg laminate consists0.95kgPET+0.05kgadhesive:95/5split is an engineering assumption; source does not specify adhesive composition/mass. Use existing adhesive-for-metal as a bonding-route proxy, not a measured fuel-cell adhesive. Assume98percent PET film retention:feed0.95/0.98kgPET,forming0.95/0.98kg extrusion andwaste0.95*(1/0.98-1)kg; adhesive100percent retained. Net retained product1kg; no sourcefilm deleted as packaging. Sensitivities glue0-10masspercent andPETretention95-100percent. PET catalyst/antimony background follows its actual supplier; no added or zeroed metal coefficient. Film role, exact adhesive cure/emissions and ultimate component end-of-life remain gaps. Generic stack lifetime/platinum/loading trajectories and all other manufacturing inputs unchanged; shared road/rail stack buyers receive the material correction through their existing manufacturing supplier.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+APPROVED PEMFC ETHOXYLATED-ALCOHOL SOURCE MATCH, 2026-10-18. Mori et al. (2023), DOI 10.1016/j.ijhydene.2023.05.255, Table 1, printed page 39676 (https://repozitorij.uni-lj.si/Dokument.php?id=178494&amp;lang=slv), specifies C12-15 Alcohol (petro) Ethoxylate, 7 mol EO, 4.58 g/kWe. Replace AE&gt;20 with existing ethoxylated alcohol (AE7) production, petrochemical, RER. Retain =4.58/1000 kg/kWe, uncertainty and all other stack inputs. This European petrochemical supplier is a chemical-class and route proxy; exact chain-length distribution and measured supply are not established. No change to stack lifetime, platinum loading or any future reduction.
 PREVIOUS NOTES (retained as history; the correction above takes precedence):
 LCI for a PEMFC fuel cell stack. Original size: 48 kWe, but normalized here to 1 kWe. Regarding geographical and time scope, production in Europe was considered based on current conditions. The reference year of the data is 2021 and data sets could be considered valid until 2024. The stack consists of 280 membrane electrode assembly (MEA) units with an active area of 200 cm2 each. The amount of Pt in the stack is 0.5425 g/kW, with a power density of 1.36 kW/kg. Operational time was set to 20,000 h at power of 1 kWe. Due to the degradation effects the hydrogen consumption must be increased to always generate the power of 1 kWe. In the case of dynamic operational regime 5 replacements (Nd = 5) of the PEMFC stack are included (lifetime of 3'800 hours per stack). Local PEMFC stack steel-identity correction, 2026-10-17 (approved). Mori et al. (2023), Life cycle sustainability assessment of a proton exchange membrane fuel cell technology for ecodesign purposes, DOI 10.1016/j.ijhydene.2023.05.255, Table 1, printed page 39676 (PDF page 4). https://repozitorij.uni-lj.si/Dokument.php?id=178494&amp;lang=slv The Steel product row reports 2.820 kg per 48 kWe stack, or 58.75 g/kWe, linked to DE: EAF Steel billet/Slab/Bloom Sphera. It is separate from the source stainless (450.47 g/kWe) and chromium-steel (17.75 g/kWe) entries. Replace only this 58.75 g input with steel production, electric, low-alloyed, Europe without Switzerland and Austria; product steel, low-alloyed. This ecoinvent European ordinary EAF-steel activity is a regional and grade proxy for the source German Sphera steel, not the identical source process or a documented exact alloy composition. Retain the original =58.75/1000 kg per 1 kWe stack formula, reference output, separate stainless inputs, steel-working service and other manufacturing coefficients. Inherited quantity uncertainty/pedigree fields are retained and do not quantify this supplier-proxy uncertainty. No added fabrication or yield factor, changed stack lifetime, or new primary/secondary trajectory. This mapping correction does not validate the complete stack, practical metal yields or suitability of the source 2021 light-vehicle design for other vehicles and future years.</t>
         </is>
@@ -1639,15 +1641,19 @@
       </c>
     </row>
     <row r="32" spans="1:20" s="12" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A32" s="12" t="s">
-        <v>113</v>
+      <c r="A32" s="12" t="inlineStr">
+        <is>
+          <t>PET adhesive film, fuel cell engineering reference</t>
+        </is>
       </c>
       <c r="B32" s="12">
         <f>37.92/1000</f>
         <v>3.7920000000000002E-2</v>
       </c>
-      <c r="C32" s="12" t="s">
-        <v>23</v>
+      <c r="C32" s="12" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
       </c>
       <c r="D32" s="12" t="s">
         <v>13</v>
@@ -1655,8 +1661,15 @@
       <c r="F32" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="G32" s="12" t="s">
-        <v>114</v>
+      <c r="G32" s="12" t="inlineStr">
+        <is>
+          <t>PET adhesive film, fuel cell engineering reference</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>APPROVED PEMFC PET-FILM MATERIAL IDENTITY, item32, 2026-10-18. Mori2023 Table1 DOI10.1016/j.ijhydene.2023.05.255 https://repozitorij.uni-lj.si/Dokument.php?id=178494&amp;lang=slv specifies37.92g PETfilmwithglue/kWe, notLDPE. Keep total film/glue purchase0.03792kg/kWe. Reference1kg laminate consists0.95kgPET+0.05kgadhesive:95/5split is an engineering assumption; source does not specify adhesive composition/mass. Use existing adhesive-for-metal as a bonding-route proxy, not a measured fuel-cell adhesive. Assume98percent PET film retention:feed0.95/0.98kgPET,forming0.95/0.98kg extrusion andwaste0.95*(1/0.98-1)kg; adhesive100percent retained. Net retained product1kg; no sourcefilm deleted as packaging. Sensitivities glue0-10masspercent andPETretention95-100percent. PET catalyst/antimony background follows its actual supplier; no added or zeroed metal coefficient. Film role, exact adhesive cure/emissions and ultimate component end-of-life remain gaps. Generic stack lifetime/platinum/loading trajectories and all other manufacturing inputs unchanged; shared road/rail stack buyers receive the material correction through their existing manufacturing supplier.</t>
+        </is>
       </c>
       <c r="I32" s="12">
         <v>2</v>
@@ -8530,6 +8543,287 @@
         </is>
       </c>
     </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>PET adhesive film, fuel cell engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B407">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>PET adhesive film, fuel cell engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>Mori2023 Table1 DOI10.1016/j.ijhydene.2023.05.255 https://repozitorij.uni-lj.si/Dokument.php?id=178494&amp;lang=slv specifies37.92g PETfilmwithglue/kWe, notLDPE.</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>APPROVED PEMFC PET-FILM MATERIAL IDENTITY, item32, 2026-10-18. Mori2023 Table1 DOI10.1016/j.ijhydene.2023.05.255 https://repozitorij.uni-lj.si/Dokument.php?id=178494&amp;lang=slv specifies37.92g PETfilmwithglue/kWe, notLDPE. Keep total film/glue purchase0.03792kg/kWe. Reference1kg laminate consists0.95kgPET+0.05kgadhesive:95/5split is an engineering assumption; source does not specify adhesive composition/mass. Use existing adhesive-for-metal as a bonding-route proxy, not a measured fuel-cell adhesive. Assume98percent PET film retention:feed0.95/0.98kgPET,forming0.95/0.98kg extrusion andwaste0.95*(1/0.98-1)kg; adhesive100percent retained. Net retained product1kg; no sourcefilm deleted as packaging. Sensitivities glue0-10masspercent andPETretention95-100percent. PET catalyst/antimony background follows its actual supplier; no added or zeroed metal coefficient. Film role, exact adhesive cure/emissions and ultimate component end-of-life remain gaps. Generic stack lifetime/platinum/loading trajectories and all other manufacturing inputs unchanged; shared road/rail stack buyers receive the material correction through their existing manufacturing supplier.</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>Exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C413" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="D413" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E413" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="F413" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="G413" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H413" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>PET adhesive film, fuel cell engineering reference</t>
+        </is>
+      </c>
+      <c r="B414">
+        <v>1</v>
+      </c>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D414" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F414" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="G414" t="inlineStr">
+        <is>
+          <t>PET adhesive film, fuel cell engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>market for polyethylene terephthalate, granulate, amorphous</t>
+        </is>
+      </c>
+      <c r="B415">
+        <v>0.9693877551020408</v>
+      </c>
+      <c r="C415" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D415" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F415" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G415" t="inlineStr">
+        <is>
+          <t>polyethylene terephthalate, granulate, amorphous</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>market for extrusion, plastic film</t>
+        </is>
+      </c>
+      <c r="B416">
+        <v>0.9693877551020408</v>
+      </c>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D416" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F416" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G416" t="inlineStr">
+        <is>
+          <t>extrusion, plastic film</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>market for adhesive, for metal</t>
+        </is>
+      </c>
+      <c r="B417">
+        <v>0.05</v>
+      </c>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D417" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F417" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G417" t="inlineStr">
+        <is>
+          <t>adhesive, for metal</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>market for waste plastic, mixture</t>
+        </is>
+      </c>
+      <c r="B418">
+        <v>-0.019387755102040837</v>
+      </c>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>CH</t>
+        </is>
+      </c>
+      <c r="D418" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F418" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G418" t="inlineStr">
+        <is>
+          <t>waste plastic, mixture</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/premise/data/additional_inventories/lci-fuel_cell.xlsx
+++ b/premise/data/additional_inventories/lci-fuel_cell.xlsx
@@ -1643,7 +1643,7 @@
     <row r="32" spans="1:20" s="12" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A32" s="12" t="inlineStr">
         <is>
-          <t>PET adhesive film, fuel cell engineering reference</t>
+          <t xml:space="preserve">polyethylene terephthalate adhesive film production, for fuel cells</t>
         </is>
       </c>
       <c r="B32" s="12">
@@ -1663,7 +1663,7 @@
       </c>
       <c r="G32" s="12" t="inlineStr">
         <is>
-          <t>PET adhesive film, fuel cell engineering reference</t>
+          <t xml:space="preserve">polyethylene terephthalate adhesive film, for fuel cells</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -7869,7 +7869,7 @@
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>fuel cell Balance of Plant, road mass engineering reference</t>
+          <t xml:space="preserve">fuel cell Balance of Plant production, road vehicle</t>
         </is>
       </c>
     </row>
@@ -7903,7 +7903,7 @@
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>fuel cell Balance of Plant, road mass engineering reference</t>
+          <t xml:space="preserve">fuel cell Balance of Plant, road vehicle</t>
         </is>
       </c>
     </row>
@@ -7939,7 +7939,8 @@
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>APPROVED ROAD FUEL-CELL AUXILIARY MASS REFERENCE, item27, 2026-10-18. Stropnik etal2022 Table1 DOI10.1016/j.ijhydene.2022.04.011 https://repozitorij.uni-lj.si/Dokument.php?id=159610&amp;lang=eng; existing vehicle exporter mass/6.6 normalization. Existing manufacturing reference contains3.7kg plainsteel+1.5HDPE+1.1stainless+0.8iron+0.75Al+0.25PP=8.1kg/kWe; exporter divides modeled physical BoP mass by6.6, omitting the HDPE from that divisor. Gross source inputs are not automatically retained mass. Adopt explicit engineering100percent material retention reference:onekg installed roadBoP is public recipe/8.1 with separately retained forming services and16.9/8.1kWh manufacture. No measured yield or manufacturer material breakdown is claimed. Replace vehicle purchaseqold units withqold*6.6kg of this mass-based reference, recovering its modeled equipment mass. This changes selected manufacturing representation;8.1/6.6 is not a proven physical-error factor or blanket correction to generic fuel-cell inventories. Model-installed BoP mass/power remains an unvalidated sizing assumption, particularly car1.347826 andtruck1.4kg/kW versus stationary/lightvehicle source8.1kg/kW; engineering transfer is composition-by-mass, not identical source functionality. Generic1kWe recipe and its purchasers remain unchanged. Existing corrected plainsteel grade and separately specified stainless preserved. No new recovery credits or primary/secondary assumptions. Stack and BoP counts are deliberately unchanged here; independent replacement budgets are item28. Test retained-mass fraction80-100percent and alternative mobile BoP composition; functional component coverage and losses remain gaps.</t>
+          <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: fuel cell Balance of Plant, road mass engineering reference. Former reference product: fuel cell Balance of Plant, road mass engineering reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
+APPROVED ROAD FUEL-CELL AUXILIARY MASS REFERENCE, item27, 2026-10-18. Stropnik etal2022 Table1 DOI10.1016/j.ijhydene.2022.04.011 https://repozitorij.uni-lj.si/Dokument.php?id=159610&amp;lang=eng; existing vehicle exporter mass/6.6 normalization. Existing manufacturing reference contains3.7kg plainsteel+1.5HDPE+1.1stainless+0.8iron+0.75Al+0.25PP=8.1kg/kWe; exporter divides modeled physical BoP mass by6.6, omitting the HDPE from that divisor. Gross source inputs are not automatically retained mass. Adopt explicit engineering100percent material retention reference:onekg installed roadBoP is public recipe/8.1 with separately retained forming services and16.9/8.1kWh manufacture. No measured yield or manufacturer material breakdown is claimed. Replace vehicle purchaseqold units withqold*6.6kg of this mass-based reference, recovering its modeled equipment mass. This changes selected manufacturing representation;8.1/6.6 is not a proven physical-error factor or blanket correction to generic fuel-cell inventories. Model-installed BoP mass/power remains an unvalidated sizing assumption, particularly car1.347826 andtruck1.4kg/kW versus stationary/lightvehicle source8.1kg/kW; engineering transfer is composition-by-mass, not identical source functionality. Generic1kWe recipe and its purchasers remain unchanged. Existing corrected plainsteel grade and separately specified stainless preserved. No new recovery credits or primary/secondary assumptions. Stack and BoP counts are deliberately unchanged here; independent replacement budgets are item28. Test retained-mass fraction80-100percent and alternative mobile BoP composition; functional component coverage and losses remain gaps.</t>
         </is>
       </c>
     </row>
@@ -7995,7 +7996,7 @@
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>fuel cell Balance of Plant, road mass engineering reference</t>
+          <t xml:space="preserve">fuel cell Balance of Plant production, road vehicle</t>
         </is>
       </c>
       <c r="B378">
@@ -8018,7 +8019,7 @@
       </c>
       <c r="G378" t="inlineStr">
         <is>
-          <t>fuel cell Balance of Plant, road mass engineering reference</t>
+          <t xml:space="preserve">fuel cell Balance of Plant, road vehicle</t>
         </is>
       </c>
     </row>
@@ -8330,7 +8331,7 @@
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>fuel cell system assembly, rail30kh stack engineering reference</t>
+          <t xml:space="preserve">fuel cell system assembly production, rail transport</t>
         </is>
       </c>
     </row>
@@ -8364,7 +8365,7 @@
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>fuel cell system assembly, rail30kh stack engineering reference</t>
+          <t xml:space="preserve">fuel cell system assembly, rail transport</t>
         </is>
       </c>
     </row>
@@ -8400,7 +8401,8 @@
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>APPROVED SINGLE RAIL FUEL-CELL REPLACEMENT BUDGET, item29, 2026-10-18. Knibbe2023 DOI10.1016/j.est.2023.108090, owner rail reference860kW/30000hstack and240000hoperation; Stropnik2022 DOI10.1016/j.ijhydene.2022.04.011 BoP20000h. Existing owner buys860kW*240000/30000=6880kW-equivalent system sets. Generic assembly additionally buys20000/3800=5.2631579stacks, yielding42.105stack sets over owner life. Introduce rail-specific assembly per1kWe owner set:one existing generic manufactured stack (not generic lifetime assembly) and30000/20000=1.5genericBoP units. Therefore owner lifetime has8stacksets and12BoPsets, each budget applied once.30000h railstack life is the existing heavy-haul engineering assumption, not a demonstrated lightvehicle stack endurance; retain it explicitly rather than silently importing3800h. BoP20000h is a source-based engineering durability proxy; fractional1.5 is expected lifetime attribution, not an instantaneous1.5BoP installation. Stack and BoP manufacture/source grades/size proxies remain unchanged; generic stack remains eligible for existing future catalyst updates. No new platinum loading or primary/secondary curve. Heavy-haul power/duty/passenger representativeness, storage and battery design remain separate gaps. Existing860kW and6880owner quantity retained; the explicit final-energy hydrogen passenger-rail purchase relinked; other rail service inherits its locomotive supplier so old cached assembly identity cannot persist.</t>
+          <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: fuel cell system assembly, rail30kh stack engineering reference. Former reference product: fuel cell system assembly, rail30kh stack engineering reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
+APPROVED SINGLE RAIL FUEL-CELL REPLACEMENT BUDGET, item29, 2026-10-18. Knibbe2023 DOI10.1016/j.est.2023.108090, owner rail reference860kW/30000hstack and240000hoperation; Stropnik2022 DOI10.1016/j.ijhydene.2022.04.011 BoP20000h. Existing owner buys860kW*240000/30000=6880kW-equivalent system sets. Generic assembly additionally buys20000/3800=5.2631579stacks, yielding42.105stack sets over owner life. Introduce rail-specific assembly per1kWe owner set:one existing generic manufactured stack (not generic lifetime assembly) and30000/20000=1.5genericBoP units. Therefore owner lifetime has8stacksets and12BoPsets, each budget applied once.30000h railstack life is the existing heavy-haul engineering assumption, not a demonstrated lightvehicle stack endurance; retain it explicitly rather than silently importing3800h. BoP20000h is a source-based engineering durability proxy; fractional1.5 is expected lifetime attribution, not an instantaneous1.5BoP installation. Stack and BoP manufacture/source grades/size proxies remain unchanged; generic stack remains eligible for existing future catalyst updates. No new platinum loading or primary/secondary curve. Heavy-haul power/duty/passenger representativeness, storage and battery design remain separate gaps. Existing860kW and6880owner quantity retained; the explicit final-energy hydrogen passenger-rail purchase relinked; other rail service inherits its locomotive supplier so old cached assembly identity cannot persist.</t>
         </is>
       </c>
     </row>
@@ -8456,7 +8458,7 @@
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>fuel cell system assembly, rail30kh stack engineering reference</t>
+          <t xml:space="preserve">fuel cell system assembly production, rail transport</t>
         </is>
       </c>
       <c r="B400">
@@ -8479,7 +8481,7 @@
       </c>
       <c r="G400" t="inlineStr">
         <is>
-          <t>fuel cell system assembly, rail30kh stack engineering reference</t>
+          <t xml:space="preserve">fuel cell system assembly, rail transport</t>
         </is>
       </c>
     </row>
@@ -8551,7 +8553,7 @@
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>PET adhesive film, fuel cell engineering reference</t>
+          <t xml:space="preserve">polyethylene terephthalate adhesive film production, for fuel cells</t>
         </is>
       </c>
     </row>
@@ -8585,7 +8587,7 @@
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>PET adhesive film, fuel cell engineering reference</t>
+          <t xml:space="preserve">polyethylene terephthalate adhesive film, for fuel cells</t>
         </is>
       </c>
     </row>
@@ -8621,7 +8623,8 @@
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>APPROVED PEMFC PET-FILM MATERIAL IDENTITY, item32, 2026-10-18. Mori2023 Table1 DOI10.1016/j.ijhydene.2023.05.255 https://repozitorij.uni-lj.si/Dokument.php?id=178494&amp;lang=slv specifies37.92g PETfilmwithglue/kWe, notLDPE. Keep total film/glue purchase0.03792kg/kWe. Reference1kg laminate consists0.95kgPET+0.05kgadhesive:95/5split is an engineering assumption; source does not specify adhesive composition/mass. Use existing adhesive-for-metal as a bonding-route proxy, not a measured fuel-cell adhesive. Assume98percent PET film retention:feed0.95/0.98kgPET,forming0.95/0.98kg extrusion andwaste0.95*(1/0.98-1)kg; adhesive100percent retained. Net retained product1kg; no sourcefilm deleted as packaging. Sensitivities glue0-10masspercent andPETretention95-100percent. PET catalyst/antimony background follows its actual supplier; no added or zeroed metal coefficient. Film role, exact adhesive cure/emissions and ultimate component end-of-life remain gaps. Generic stack lifetime/platinum/loading trajectories and all other manufacturing inputs unchanged; shared road/rail stack buyers receive the material correction through their existing manufacturing supplier.</t>
+          <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: PET adhesive film, fuel cell engineering reference. Former reference product: PET adhesive film, fuel cell engineering reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
+APPROVED PEMFC PET-FILM MATERIAL IDENTITY, item32, 2026-10-18. Mori2023 Table1 DOI10.1016/j.ijhydene.2023.05.255 https://repozitorij.uni-lj.si/Dokument.php?id=178494&amp;lang=slv specifies37.92g PETfilmwithglue/kWe, notLDPE. Keep total film/glue purchase0.03792kg/kWe. Reference1kg laminate consists0.95kgPET+0.05kgadhesive:95/5split is an engineering assumption; source does not specify adhesive composition/mass. Use existing adhesive-for-metal as a bonding-route proxy, not a measured fuel-cell adhesive. Assume98percent PET film retention:feed0.95/0.98kgPET,forming0.95/0.98kg extrusion andwaste0.95*(1/0.98-1)kg; adhesive100percent retained. Net retained product1kg; no sourcefilm deleted as packaging. Sensitivities glue0-10masspercent andPETretention95-100percent. PET catalyst/antimony background follows its actual supplier; no added or zeroed metal coefficient. Film role, exact adhesive cure/emissions and ultimate component end-of-life remain gaps. Generic stack lifetime/platinum/loading trajectories and all other manufacturing inputs unchanged; shared road/rail stack buyers receive the material correction through their existing manufacturing supplier.</t>
         </is>
       </c>
     </row>
@@ -8677,7 +8680,7 @@
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>PET adhesive film, fuel cell engineering reference</t>
+          <t xml:space="preserve">polyethylene terephthalate adhesive film production, for fuel cells</t>
         </is>
       </c>
       <c r="B414">
@@ -8700,7 +8703,7 @@
       </c>
       <c r="G414" t="inlineStr">
         <is>
-          <t>PET adhesive film, fuel cell engineering reference</t>
+          <t xml:space="preserve">polyethylene terephthalate adhesive film, for fuel cells</t>
         </is>
       </c>
     </row>

--- a/premise/data/additional_inventories/lci-fuel_cell.xlsx
+++ b/premise/data/additional_inventories/lci-fuel_cell.xlsx
@@ -8331,7 +8331,7 @@
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t xml:space="preserve">fuel cell system assembly production, rail transport</t>
+          <t xml:space="preserve">fuel cell system assembly production, rail transport, 860 kWe</t>
         </is>
       </c>
     </row>
@@ -8365,7 +8365,7 @@
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t xml:space="preserve">fuel cell system assembly, rail transport</t>
+          <t xml:space="preserve">fuel cell system assembly, rail transport, 860 kWe</t>
         </is>
       </c>
     </row>
@@ -8401,7 +8401,8 @@
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: fuel cell system assembly, rail30kh stack engineering reference. Former reference product: fuel cell system assembly, rail30kh stack engineering reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
+          <t xml:space="preserve">APPROVED REFERENCE-UNIT CORRECTION, 2026-10-19. Current reference: One complete 860 kWe rail fuel-cell system, retaining the existing stack/BoP replacement attribution. Unit field: unit. Former reference: 1 unit = 0.0011627906976744186 unit on the current basis. All supplier/product references and direct purchasers are updated together. Recipes are divided by this conversion factor and consumer doses multiplied by it; physical inputs, emissions and waste per original functional unit are preserved. One complete 860 kWe system uses 860 one-kWe stack references and 1290 one-kWe BoP references over the existing 30000 h stack interval. The locomotive buys eight lifetime system sets, preserving eight full-power stack sets and twelve full-power BoP sets. Its per-MJ purchase and structured allocation provenance are divided by 860. Fractional BoP remains expected lifetime attribution. No new unit vocabulary, design, lifetime, manufacturing yield, recycling credit, primary/secondary share or runtime code change. Earlier source notes below retain their historical normalization; the current reference and amounts above supersede that normalization.
+Nomenclature revision, 2026-10-19. Former activity name: fuel cell system assembly, rail30kh stack engineering reference. Former reference product: fuel cell system assembly, rail30kh stack engineering reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
 APPROVED SINGLE RAIL FUEL-CELL REPLACEMENT BUDGET, item29, 2026-10-18. Knibbe2023 DOI10.1016/j.est.2023.108090, owner rail reference860kW/30000hstack and240000hoperation; Stropnik2022 DOI10.1016/j.ijhydene.2022.04.011 BoP20000h. Existing owner buys860kW*240000/30000=6880kW-equivalent system sets. Generic assembly additionally buys20000/3800=5.2631579stacks, yielding42.105stack sets over owner life. Introduce rail-specific assembly per1kWe owner set:one existing generic manufactured stack (not generic lifetime assembly) and30000/20000=1.5genericBoP units. Therefore owner lifetime has8stacksets and12BoPsets, each budget applied once.30000h railstack life is the existing heavy-haul engineering assumption, not a demonstrated lightvehicle stack endurance; retain it explicitly rather than silently importing3800h. BoP20000h is a source-based engineering durability proxy; fractional1.5 is expected lifetime attribution, not an instantaneous1.5BoP installation. Stack and BoP manufacture/source grades/size proxies remain unchanged; generic stack remains eligible for existing future catalyst updates. No new platinum loading or primary/secondary curve. Heavy-haul power/duty/passenger representativeness, storage and battery design remain separate gaps. Existing860kW and6880owner quantity retained; the explicit final-energy hydrogen passenger-rail purchase relinked; other rail service inherits its locomotive supplier so old cached assembly identity cannot persist.</t>
         </is>
       </c>
@@ -8458,7 +8459,7 @@
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t xml:space="preserve">fuel cell system assembly production, rail transport</t>
+          <t xml:space="preserve">fuel cell system assembly production, rail transport, 860 kWe</t>
         </is>
       </c>
       <c r="B400">
@@ -8481,7 +8482,7 @@
       </c>
       <c r="G400" t="inlineStr">
         <is>
-          <t xml:space="preserve">fuel cell system assembly, rail transport</t>
+          <t xml:space="preserve">fuel cell system assembly, rail transport, 860 kWe</t>
         </is>
       </c>
     </row>
@@ -8492,7 +8493,7 @@
         </is>
       </c>
       <c r="B401">
-        <v>1</v>
+        <v>860.0</v>
       </c>
       <c r="C401" t="inlineStr">
         <is>
@@ -8522,7 +8523,7 @@
         </is>
       </c>
       <c r="B402">
-        <v>1.5</v>
+        <v>1290.0</v>
       </c>
       <c r="C402" t="inlineStr">
         <is>

--- a/premise/data/additional_inventories/lci-fuel_cell.xlsx
+++ b/premise/data/additional_inventories/lci-fuel_cell.xlsx
@@ -857,7 +857,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:T418"/>
+  <dimension ref="A1:T421"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="41.1640625" customWidth="1"/>
@@ -7869,7 +7869,7 @@
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t xml:space="preserve">fuel cell Balance of Plant production, road vehicle</t>
+          <t xml:space="preserve">fuel cell balance of plant production, road vehicle</t>
         </is>
       </c>
     </row>
@@ -7947,94 +7947,76 @@
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>Exchanges</t>
+          <t xml:space="preserve">type</t>
+        </is>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t xml:space="preserve">processwithreferenceproduct</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="B377" t="inlineStr">
-        <is>
-          <t>amount</t>
-        </is>
-      </c>
-      <c r="C377" t="inlineStr">
-        <is>
-          <t>location</t>
-        </is>
-      </c>
-      <c r="D377" t="inlineStr">
-        <is>
-          <t>unit</t>
-        </is>
-      </c>
-      <c r="E377" t="inlineStr">
-        <is>
-          <t>categories</t>
-        </is>
-      </c>
-      <c r="F377" t="inlineStr">
-        <is>
-          <t>type</t>
-        </is>
-      </c>
-      <c r="G377" t="inlineStr">
-        <is>
-          <t>reference product</t>
-        </is>
-      </c>
-      <c r="H377" t="inlineStr">
-        <is>
-          <t>comment</t>
+          <t>Exchanges</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t xml:space="preserve">fuel cell Balance of Plant production, road vehicle</t>
-        </is>
-      </c>
-      <c r="B378">
-        <v>1</v>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>GLO</t>
+          <t>location</t>
         </is>
       </c>
       <c r="D378" t="inlineStr">
         <is>
-          <t>kilogram</t>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E378" t="inlineStr">
+        <is>
+          <t>categories</t>
         </is>
       </c>
       <c r="F378" t="inlineStr">
         <is>
-          <t>production</t>
+          <t>type</t>
         </is>
       </c>
       <c r="G378" t="inlineStr">
         <is>
-          <t xml:space="preserve">fuel cell Balance of Plant, road vehicle</t>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H378" t="inlineStr">
+        <is>
+          <t>comment</t>
         </is>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>steel production, electric, low-alloyed</t>
+          <t xml:space="preserve">fuel cell balance of plant production, road vehicle</t>
         </is>
       </c>
       <c r="B379">
-        <v>0.45679012345679015</v>
+        <v>1</v>
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>Europe without Switzerland and Austria</t>
+          <t>GLO</t>
         </is>
       </c>
       <c r="D379" t="inlineStr">
@@ -8044,19 +8026,19 @@
       </c>
       <c r="F379" t="inlineStr">
         <is>
-          <t>technosphere</t>
+          <t>production</t>
         </is>
       </c>
       <c r="G379" t="inlineStr">
         <is>
-          <t>steel, low-alloyed</t>
+          <t xml:space="preserve">fuel cell Balance of Plant, road vehicle</t>
         </is>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>market for metal working, average for steel product manufacturing</t>
+          <t>steel production, electric, low-alloyed</t>
         </is>
       </c>
       <c r="B380">
@@ -8064,7 +8046,7 @@
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>GLO</t>
+          <t>Europe without Switzerland and Austria</t>
         </is>
       </c>
       <c r="D380" t="inlineStr">
@@ -8079,18 +8061,18 @@
       </c>
       <c r="G380" t="inlineStr">
         <is>
-          <t>metal working, average for steel product manufacturing</t>
+          <t>steel, low-alloyed</t>
         </is>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>market for polyethylene, high density, granulate</t>
+          <t>market for metal working, average for steel product manufacturing</t>
         </is>
       </c>
       <c r="B381">
-        <v>0.1851851851851852</v>
+        <v>0.45679012345679015</v>
       </c>
       <c r="C381" t="inlineStr">
         <is>
@@ -8109,18 +8091,18 @@
       </c>
       <c r="G381" t="inlineStr">
         <is>
-          <t>polyethylene, high density, granulate</t>
+          <t>metal working, average for steel product manufacturing</t>
         </is>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>market for steel, chromium steel 18/8</t>
+          <t>market for polyethylene, high density, granulate</t>
         </is>
       </c>
       <c r="B382">
-        <v>0.1358024691358025</v>
+        <v>0.1851851851851852</v>
       </c>
       <c r="C382" t="inlineStr">
         <is>
@@ -8139,14 +8121,14 @@
       </c>
       <c r="G382" t="inlineStr">
         <is>
-          <t>steel, chromium steel 18/8</t>
+          <t>polyethylene, high density, granulate</t>
         </is>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>market for metal working, average for steel product manufacturing</t>
+          <t>market for steel, chromium steel 18/8</t>
         </is>
       </c>
       <c r="B383">
@@ -8169,18 +8151,18 @@
       </c>
       <c r="G383" t="inlineStr">
         <is>
-          <t>metal working, average for steel product manufacturing</t>
+          <t>steel, chromium steel 18/8</t>
         </is>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>market for cast iron</t>
+          <t>market for metal working, average for steel product manufacturing</t>
         </is>
       </c>
       <c r="B384">
-        <v>0.09876543209876544</v>
+        <v>0.1358024691358025</v>
       </c>
       <c r="C384" t="inlineStr">
         <is>
@@ -8199,22 +8181,22 @@
       </c>
       <c r="G384" t="inlineStr">
         <is>
-          <t>cast iron</t>
+          <t>metal working, average for steel product manufacturing</t>
         </is>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>market for aluminium, primary, ingot</t>
+          <t>market for cast iron</t>
         </is>
       </c>
       <c r="B385">
-        <v>0.0925925925925926</v>
+        <v>0.09876543209876544</v>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>IAI Area, EU27 &amp; EFTA</t>
+          <t>GLO</t>
         </is>
       </c>
       <c r="D385" t="inlineStr">
@@ -8229,14 +8211,14 @@
       </c>
       <c r="G385" t="inlineStr">
         <is>
-          <t>aluminium, primary, ingot</t>
+          <t>cast iron</t>
         </is>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>market for metal working, average for aluminium product manufacturing</t>
+          <t>market for aluminium, primary, ingot</t>
         </is>
       </c>
       <c r="B386">
@@ -8244,7 +8226,7 @@
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>GLO</t>
+          <t>IAI Area, EU27 &amp; EFTA</t>
         </is>
       </c>
       <c r="D386" t="inlineStr">
@@ -8259,18 +8241,18 @@
       </c>
       <c r="G386" t="inlineStr">
         <is>
-          <t>metal working, average for aluminium product manufacturing</t>
+          <t>aluminium, primary, ingot</t>
         </is>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>market for polypropylene, granulate</t>
+          <t>market for metal working, average for aluminium product manufacturing</t>
         </is>
       </c>
       <c r="B387">
-        <v>0.0308641975308642</v>
+        <v>0.0925925925925926</v>
       </c>
       <c r="C387" t="inlineStr">
         <is>
@@ -8289,117 +8271,147 @@
       </c>
       <c r="G387" t="inlineStr">
         <is>
-          <t>polypropylene, granulate</t>
+          <t>metal working, average for aluminium product manufacturing</t>
         </is>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
+          <t>market for polypropylene, granulate</t>
+        </is>
+      </c>
+      <c r="B388">
+        <v>0.0308641975308642</v>
+      </c>
+      <c r="C388" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F388" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G388" t="inlineStr">
+        <is>
+          <t>polypropylene, granulate</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
           <t>market group for electricity, low voltage</t>
         </is>
       </c>
-      <c r="B388">
+      <c r="B389">
         <v>2.0864197530864197</v>
       </c>
-      <c r="C388" t="inlineStr">
+      <c r="C389" t="inlineStr">
         <is>
           <t>GLO</t>
         </is>
       </c>
-      <c r="D388" t="inlineStr">
+      <c r="D389" t="inlineStr">
         <is>
           <t>kilowatt hour</t>
         </is>
       </c>
-      <c r="F388" t="inlineStr">
+      <c r="F389" t="inlineStr">
         <is>
           <t>technosphere</t>
         </is>
       </c>
-      <c r="G388" t="inlineStr">
+      <c r="G389" t="inlineStr">
         <is>
           <t>electricity, low voltage</t>
-        </is>
-      </c>
-    </row>
-    <row r="391">
-      <c r="A391" t="inlineStr">
-        <is>
-          <t>Activity</t>
-        </is>
-      </c>
-      <c r="B391" t="inlineStr">
-        <is>
-          <t xml:space="preserve">fuel cell system assembly production, rail transport, 860 kWe</t>
         </is>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>location</t>
+          <t>Activity</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>GLO</t>
+          <t xml:space="preserve">fuel cell system assembly production, rail transport, 860 kwe</t>
         </is>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>production amount</t>
-        </is>
-      </c>
-      <c r="B393">
-        <v>1</v>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>reference product</t>
-        </is>
-      </c>
-      <c r="B394" t="inlineStr">
-        <is>
-          <t xml:space="preserve">fuel cell system assembly, rail transport, 860 kWe</t>
-        </is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B394">
+        <v>1</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t>reference product</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t xml:space="preserve">fuel cell system assembly, rail transport, 860 kWe</t>
         </is>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>source</t>
+          <t>unit</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>Knibbe2023 DOI10.1016/j.est.2023.108090, owner rail reference860kW/30000hstack and240000hoperation; Stropnik2022 DOI10.1016/j.ijhydene.2022.04.011 BoP20000h.</t>
+          <t>unit</t>
         </is>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>Knibbe2023 DOI10.1016/j.est.2023.108090, owner rail reference860kW/30000hstack and240000hoperation; Stropnik2022 DOI10.1016/j.ijhydene.2022.04.011 BoP20000h.</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
           <t>comment</t>
         </is>
       </c>
-      <c r="B397" t="inlineStr">
+      <c r="B398" t="inlineStr">
         <is>
           <t xml:space="preserve">APPROVED REFERENCE-UNIT CORRECTION, 2026-10-19. Current reference: One complete 860 kWe rail fuel-cell system, retaining the existing stack/BoP replacement attribution. Unit field: unit. Former reference: 1 unit = 0.0011627906976744186 unit on the current basis. All supplier/product references and direct purchasers are updated together. Recipes are divided by this conversion factor and consumer doses multiplied by it; physical inputs, emissions and waste per original functional unit are preserved. One complete 860 kWe system uses 860 one-kWe stack references and 1290 one-kWe BoP references over the existing 30000 h stack interval. The locomotive buys eight lifetime system sets, preserving eight full-power stack sets and twelve full-power BoP sets. Its per-MJ purchase and structured allocation provenance are divided by 860. Fractional BoP remains expected lifetime attribution. No new unit vocabulary, design, lifetime, manufacturing yield, recycling credit, primary/secondary share or runtime code change. Earlier source notes below retain their historical normalization; the current reference and amounts above supersede that normalization.
 Nomenclature revision, 2026-10-19. Former activity name: fuel cell system assembly, rail30kh stack engineering reference. Former reference product: fuel cell system assembly, rail30kh stack engineering reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
@@ -8407,97 +8419,39 @@
         </is>
       </c>
     </row>
-    <row r="398">
-      <c r="A398" t="inlineStr">
-        <is>
-          <t>Exchanges</t>
-        </is>
-      </c>
-    </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>name</t>
+          <t xml:space="preserve">type</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>amount</t>
-        </is>
-      </c>
-      <c r="C399" t="inlineStr">
-        <is>
-          <t>location</t>
-        </is>
-      </c>
-      <c r="D399" t="inlineStr">
-        <is>
-          <t>unit</t>
-        </is>
-      </c>
-      <c r="E399" t="inlineStr">
-        <is>
-          <t>categories</t>
-        </is>
-      </c>
-      <c r="F399" t="inlineStr">
-        <is>
-          <t>type</t>
-        </is>
-      </c>
-      <c r="G399" t="inlineStr">
-        <is>
-          <t>reference product</t>
-        </is>
-      </c>
-      <c r="H399" t="inlineStr">
-        <is>
-          <t>comment</t>
+          <t xml:space="preserve">processwithreferenceproduct</t>
         </is>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t xml:space="preserve">fuel cell system assembly production, rail transport, 860 kWe</t>
-        </is>
-      </c>
-      <c r="B400">
-        <v>1</v>
-      </c>
-      <c r="C400" t="inlineStr">
-        <is>
-          <t>GLO</t>
-        </is>
-      </c>
-      <c r="D400" t="inlineStr">
-        <is>
-          <t>unit</t>
-        </is>
-      </c>
-      <c r="F400" t="inlineStr">
-        <is>
-          <t>production</t>
-        </is>
-      </c>
-      <c r="G400" t="inlineStr">
-        <is>
-          <t xml:space="preserve">fuel cell system assembly, rail transport, 860 kWe</t>
+          <t>Exchanges</t>
         </is>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>fuel cell stack production, 1 kWe, proton exchange membrane (PEM)</t>
-        </is>
-      </c>
-      <c r="B401">
-        <v>860.0</v>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>GLO</t>
+          <t>location</t>
         </is>
       </c>
       <c r="D401" t="inlineStr">
@@ -8505,281 +8459,273 @@
           <t>unit</t>
         </is>
       </c>
+      <c r="E401" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
       <c r="F401" t="inlineStr">
         <is>
-          <t>technosphere</t>
+          <t>type</t>
         </is>
       </c>
       <c r="G401" t="inlineStr">
         <is>
-          <t>fuel cell stack, 1 kWe, proton exchange membrane (PEM)</t>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H401" t="inlineStr">
+        <is>
+          <t>comment</t>
         </is>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
+          <t xml:space="preserve">fuel cell system assembly production, rail transport, 860 kwe</t>
+        </is>
+      </c>
+      <c r="B402">
+        <v>1</v>
+      </c>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D402" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="F402" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="G402" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fuel cell system assembly, rail transport, 860 kWe</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>fuel cell stack production, 1 kWe, proton exchange membrane (PEM)</t>
+        </is>
+      </c>
+      <c r="B403">
+        <v>860.0</v>
+      </c>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D403" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="F403" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G403" t="inlineStr">
+        <is>
+          <t>fuel cell stack, 1 kWe, proton exchange membrane (PEM)</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
           <t>fuel cell Balance of Plant production, 1 kWe, proton exchange membrane (PEM)</t>
         </is>
       </c>
-      <c r="B402">
+      <c r="B404">
         <v>1290.0</v>
       </c>
-      <c r="C402" t="inlineStr">
+      <c r="C404" t="inlineStr">
         <is>
           <t>GLO</t>
         </is>
       </c>
-      <c r="D402" t="inlineStr">
+      <c r="D404" t="inlineStr">
         <is>
           <t>unit</t>
         </is>
       </c>
-      <c r="F402" t="inlineStr">
+      <c r="F404" t="inlineStr">
         <is>
           <t>technosphere</t>
         </is>
       </c>
-      <c r="G402" t="inlineStr">
+      <c r="G404" t="inlineStr">
         <is>
           <t>fuel cell Balance of Plant, 1 kWe, proton exchange membrane (PEM)</t>
-        </is>
-      </c>
-    </row>
-    <row r="405">
-      <c r="A405" t="inlineStr">
-        <is>
-          <t>Activity</t>
-        </is>
-      </c>
-      <c r="B405" t="inlineStr">
-        <is>
-          <t xml:space="preserve">polyethylene terephthalate adhesive film production, for fuel cells</t>
-        </is>
-      </c>
-    </row>
-    <row r="406">
-      <c r="A406" t="inlineStr">
-        <is>
-          <t>location</t>
-        </is>
-      </c>
-      <c r="B406" t="inlineStr">
-        <is>
-          <t>GLO</t>
         </is>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>production amount</t>
-        </is>
-      </c>
-      <c r="B407">
-        <v>1</v>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t xml:space="preserve">polyethylene terephthalate adhesive film production, for fuel cells</t>
+        </is>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>reference product</t>
+          <t>location</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t xml:space="preserve">polyethylene terephthalate adhesive film, for fuel cells</t>
+          <t>GLO</t>
         </is>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>unit</t>
-        </is>
-      </c>
-      <c r="B409" t="inlineStr">
-        <is>
-          <t>kilogram</t>
-        </is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B409">
+        <v>1</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>source</t>
+          <t>reference product</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>Mori2023 Table1 DOI10.1016/j.ijhydene.2023.05.255 https://repozitorij.uni-lj.si/Dokument.php?id=178494&amp;lang=slv specifies37.92g PETfilmwithglue/kWe, notLDPE.</t>
+          <t xml:space="preserve">polyethylene terephthalate adhesive film, for fuel cells</t>
         </is>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>Mori2023 Table1 DOI10.1016/j.ijhydene.2023.05.255 https://repozitorij.uni-lj.si/Dokument.php?id=178494&amp;lang=slv specifies37.92g PETfilmwithglue/kWe, notLDPE.</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
           <t>comment</t>
         </is>
       </c>
-      <c r="B411" t="inlineStr">
+      <c r="B413" t="inlineStr">
         <is>
           <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: PET adhesive film, fuel cell engineering reference. Former reference product: PET adhesive film, fuel cell engineering reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
 APPROVED PEMFC PET-FILM MATERIAL IDENTITY, item32, 2026-10-18. Mori2023 Table1 DOI10.1016/j.ijhydene.2023.05.255 https://repozitorij.uni-lj.si/Dokument.php?id=178494&amp;lang=slv specifies37.92g PETfilmwithglue/kWe, notLDPE. Keep total film/glue purchase0.03792kg/kWe. Reference1kg laminate consists0.95kgPET+0.05kgadhesive:95/5split is an engineering assumption; source does not specify adhesive composition/mass. Use existing adhesive-for-metal as a bonding-route proxy, not a measured fuel-cell adhesive. Assume98percent PET film retention:feed0.95/0.98kgPET,forming0.95/0.98kg extrusion andwaste0.95*(1/0.98-1)kg; adhesive100percent retained. Net retained product1kg; no sourcefilm deleted as packaging. Sensitivities glue0-10masspercent andPETretention95-100percent. PET catalyst/antimony background follows its actual supplier; no added or zeroed metal coefficient. Film role, exact adhesive cure/emissions and ultimate component end-of-life remain gaps. Generic stack lifetime/platinum/loading trajectories and all other manufacturing inputs unchanged; shared road/rail stack buyers receive the material correction through their existing manufacturing supplier.</t>
         </is>
       </c>
     </row>
-    <row r="412">
-      <c r="A412" t="inlineStr">
-        <is>
-          <t>Exchanges</t>
-        </is>
-      </c>
-    </row>
-    <row r="413">
-      <c r="A413" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="B413" t="inlineStr">
-        <is>
-          <t>amount</t>
-        </is>
-      </c>
-      <c r="C413" t="inlineStr">
-        <is>
-          <t>location</t>
-        </is>
-      </c>
-      <c r="D413" t="inlineStr">
-        <is>
-          <t>unit</t>
-        </is>
-      </c>
-      <c r="E413" t="inlineStr">
-        <is>
-          <t>categories</t>
-        </is>
-      </c>
-      <c r="F413" t="inlineStr">
-        <is>
-          <t>type</t>
-        </is>
-      </c>
-      <c r="G413" t="inlineStr">
-        <is>
-          <t>reference product</t>
-        </is>
-      </c>
-      <c r="H413" t="inlineStr">
-        <is>
-          <t>comment</t>
-        </is>
-      </c>
-    </row>
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t xml:space="preserve">polyethylene terephthalate adhesive film production, for fuel cells</t>
-        </is>
-      </c>
-      <c r="B414">
-        <v>1</v>
-      </c>
-      <c r="C414" t="inlineStr">
-        <is>
-          <t>GLO</t>
-        </is>
-      </c>
-      <c r="D414" t="inlineStr">
-        <is>
-          <t>kilogram</t>
-        </is>
-      </c>
-      <c r="F414" t="inlineStr">
-        <is>
-          <t>production</t>
-        </is>
-      </c>
-      <c r="G414" t="inlineStr">
-        <is>
-          <t xml:space="preserve">polyethylene terephthalate adhesive film, for fuel cells</t>
+          <t xml:space="preserve">type</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t xml:space="preserve">processwithreferenceproduct</t>
         </is>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>market for polyethylene terephthalate, granulate, amorphous</t>
-        </is>
-      </c>
-      <c r="B415">
-        <v>0.9693877551020408</v>
-      </c>
-      <c r="C415" t="inlineStr">
-        <is>
-          <t>GLO</t>
-        </is>
-      </c>
-      <c r="D415" t="inlineStr">
-        <is>
-          <t>kilogram</t>
-        </is>
-      </c>
-      <c r="F415" t="inlineStr">
-        <is>
-          <t>technosphere</t>
-        </is>
-      </c>
-      <c r="G415" t="inlineStr">
-        <is>
-          <t>polyethylene terephthalate, granulate, amorphous</t>
+          <t>Exchanges</t>
         </is>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>market for extrusion, plastic film</t>
-        </is>
-      </c>
-      <c r="B416">
-        <v>0.9693877551020408</v>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>GLO</t>
+          <t>location</t>
         </is>
       </c>
       <c r="D416" t="inlineStr">
         <is>
-          <t>kilogram</t>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E416" t="inlineStr">
+        <is>
+          <t>categories</t>
         </is>
       </c>
       <c r="F416" t="inlineStr">
         <is>
-          <t>technosphere</t>
+          <t>type</t>
         </is>
       </c>
       <c r="G416" t="inlineStr">
         <is>
-          <t>extrusion, plastic film</t>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H416" t="inlineStr">
+        <is>
+          <t>comment</t>
         </is>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>market for adhesive, for metal</t>
+          <t xml:space="preserve">polyethylene terephthalate adhesive film production, for fuel cells</t>
         </is>
       </c>
       <c r="B417">
-        <v>0.05</v>
+        <v>1</v>
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>RER</t>
+          <t>GLO</t>
         </is>
       </c>
       <c r="D417" t="inlineStr">
@@ -8789,40 +8735,130 @@
       </c>
       <c r="F417" t="inlineStr">
         <is>
-          <t>technosphere</t>
+          <t>production</t>
         </is>
       </c>
       <c r="G417" t="inlineStr">
         <is>
-          <t>adhesive, for metal</t>
+          <t xml:space="preserve">polyethylene terephthalate adhesive film, for fuel cells</t>
         </is>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
+          <t>market for polyethylene terephthalate, granulate, amorphous</t>
+        </is>
+      </c>
+      <c r="B418">
+        <v>0.9693877551020408</v>
+      </c>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D418" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F418" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G418" t="inlineStr">
+        <is>
+          <t>polyethylene terephthalate, granulate, amorphous</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>market for extrusion, plastic film</t>
+        </is>
+      </c>
+      <c r="B419">
+        <v>0.9693877551020408</v>
+      </c>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F419" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G419" t="inlineStr">
+        <is>
+          <t>extrusion, plastic film</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>market for adhesive, for metal</t>
+        </is>
+      </c>
+      <c r="B420">
+        <v>0.05</v>
+      </c>
+      <c r="C420" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F420" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G420" t="inlineStr">
+        <is>
+          <t>adhesive, for metal</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
           <t>market for waste plastic, mixture</t>
         </is>
       </c>
-      <c r="B418">
+      <c r="B421">
         <v>-0.019387755102040837</v>
       </c>
-      <c r="C418" t="inlineStr">
+      <c r="C421" t="inlineStr">
         <is>
           <t>CH</t>
         </is>
       </c>
-      <c r="D418" t="inlineStr">
+      <c r="D421" t="inlineStr">
         <is>
           <t>kilogram</t>
         </is>
       </c>
-      <c r="F418" t="inlineStr">
+      <c r="F421" t="inlineStr">
         <is>
           <t>technosphere</t>
         </is>
       </c>
-      <c r="G418" t="inlineStr">
+      <c r="G421" t="inlineStr">
         <is>
           <t>waste plastic, mixture</t>
         </is>
